--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -524,10 +524,10 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>87.88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H3">
         <v>8.699999999999999</v>
@@ -609,16 +609,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>92.5</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,19 +632,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,16 +661,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +738,7 @@
         <v>92.5</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,7 +749,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -749,13 +758,13 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>87.88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,7 +790,7 @@
         <v>78.95</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,19 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ESTEPHANY SOPHIA</t>
   </si>
   <si>
     <t>ARANZA DANAE</t>
@@ -800,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,47 +823,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920362</v>
+        <v>21330051920044</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920044</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ARANZA DANAE</t>
   </si>
 </sst>
 </file>
@@ -729,7 +720,7 @@
         <v>92.5</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -772,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="H4">
         <v>8.199999999999999</v>
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -821,29 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920044</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
